--- a/调度及腾讯字段解析.xlsx
+++ b/调度及腾讯字段解析.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\pyprj\stock2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEA04730-F995-4E08-BA41-6E22CAB7C0D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB6BE59D-6FFE-440B-96D2-1642226BD9AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{1FEC2500-66C5-48E4-A19C-F08A664BA3B3}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="180">
   <si>
     <t>市场状态</t>
   </si>
@@ -306,10 +306,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>刷新频率</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>D:\pyprj\stock2\crawldata\crawl_stock.py</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -390,14 +386,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>对应的配置文件</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>.sch_config.json</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>get_qq_quotes_df</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -422,18 +410,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>.sch_config.json; .sch_qt5min.json</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>.sch_week.json</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>月,手工调度</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>fetch_qt_web</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -478,10 +454,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>TS的限售股解禁</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>D:\pyprj\stock2\crawldata\crawl_qq_fq.py</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -490,10 +462,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>手工调度</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>腾讯的复权数据。Adjust: qfq:前复权;qfq:前复权;none不复权，返回df</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -546,10 +514,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>腾讯实时个股数据。调用10号，调度所有个股的实时数据</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>fetch_qq_one_kline_db</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -558,10 +522,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>天,实时</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>get_ak_companyinfo</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -590,10 +550,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>巨潮的公司基本信息。批量获取，调用22</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>巨潮的公司基本信息。可以使用list参数调度，保存到DB</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -606,15 +562,109 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>巨潮的分红数据。</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>包装到fetch_week_data中，天调度是补充新增的，指定调度是更新已有的</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>用于初始化的；每天补充缺失的公司信息</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>按需调度</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>初始化</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>按天调度</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>按月调度</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>实时数据</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>实时</t>
+  </si>
+  <si>
+    <t>按自选股</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>天：.sch_config.json；按需：python crawldata/reflush_watchlist.py；月：基本就是初始化操作了；实时： .sch_qt5min.json</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>天：每天正常调度数据；按需：根据自选股清单进行手工调度；月：不经常更新，基本等同初始化；实时：需要重点盯盘的数据。</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>python crawldata/scheduler.py sch_config/.sch_config.json</t>
+  </si>
+  <si>
+    <t>python crawldata/scheduler.py sch_config/.sch_config.json</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>get_ak_gd_num</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TS解禁股本</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>天(被巨潮数据替代)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>巨潮解禁股本。（调度范围：从今天开始，+7天）</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>get_ak_Reduce</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>巨潮减持数据。（调度范围：过去的最近一个月）</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>get_ak_Increase</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>巨潮增持数据。（调度范围：过去的最近一个月）</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>get_ak_pfmc_frcst</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>巨潮的分红数据。（从2024年开始的数据已经调度，按报告年份）</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>巨潮股东人数及持股集中度。（从2024年开始的数据已经调度，按报告年份）</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>巨潮业绩预测数据。（调度范围：按报告年份）</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>腾讯实时个股数据。调用10号，(范围：codes的list清单，或则全部)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>巨潮的公司基本信息。批量获取，调用22（调度范围，动态：补充确实的股票）</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -669,13 +719,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="HarmonyOS Sans SC"/>
       <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <color theme="1"/>
       <name val="HarmonyOS Sans SC"/>
@@ -1810,581 +1861,716 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2885176E-875C-420E-9376-FD5A86DAD936}">
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="9"/>
-    <col min="2" max="2" width="36" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.88671875" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.44140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="61.109375" style="9" customWidth="1"/>
-    <col min="6" max="6" width="9.5546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="9"/>
+    <col min="1" max="1" width="8.88671875" style="8"/>
+    <col min="2" max="2" width="36" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="61.109375" style="8" customWidth="1"/>
+    <col min="6" max="6" width="9.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="9.5546875" style="8" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="8" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B1" s="8" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B2" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="8">
+        <v>1</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="8">
+        <v>2</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="8">
+        <v>3</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="F1" s="8" t="s">
+      <c r="E6" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="8">
+        <v>4</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="C7" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="8">
+        <v>5</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="8">
+        <v>6</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="8">
+        <v>7</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="8">
+        <v>8</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="8">
+        <v>9</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="8">
+        <v>10</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="8">
+        <v>11</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="E14" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="8">
+        <v>12</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="8">
+        <v>13</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="E16" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="I1" s="8" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="9">
-        <v>1</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="D2" s="9" t="s">
+      <c r="F16" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="8">
+        <v>14</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="F17" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="J17" s="8" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="8">
+        <v>15</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="8">
+        <v>16</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="8">
+        <v>17</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="8">
+        <v>18</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="F21" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="F2" s="9" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="9">
-        <v>2</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="E3" s="9" t="s">
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="8">
+        <v>19</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="8">
+        <v>20</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="8">
+        <v>21</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="8">
+        <v>22</v>
+      </c>
+      <c r="B25" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="9">
-        <v>3</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="9">
-        <v>4</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="9">
-        <v>5</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="9">
-        <v>6</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="9">
-        <v>7</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="9">
-        <v>8</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="9">
-        <v>9</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="E10" s="9" t="s">
+      <c r="C25" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="8">
+        <v>23</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D26" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="F10" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="9">
-        <v>10</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="E11" s="9" t="s">
+      <c r="E26" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="F11" s="9" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="9">
-        <v>11</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="E12" s="9" t="s">
+      <c r="F26" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="8">
+        <v>24</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D27" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="E27" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="8">
+        <v>25</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D28" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="G12" s="9" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="9">
-        <v>12</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="9">
-        <v>13</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="9">
-        <v>14</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="D15" s="9" t="s">
+      <c r="E28" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="8">
+        <v>26</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="8">
+        <v>27</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D30" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="E15" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="9">
-        <v>15</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="9">
-        <v>16</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="9">
-        <v>17</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="9">
-        <v>18</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="9">
-        <v>19</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="I20" s="9" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="9">
-        <v>20</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="I21" s="9" t="s">
+      <c r="E30" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="8">
+        <v>28</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="C31" s="8" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="9">
-        <v>21</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="9">
-        <v>22</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="I23" s="9" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="9">
-        <v>23</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="9">
-        <v>24</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="I25" s="9" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="9">
-        <v>25</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>164</v>
+      <c r="D31" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="8">
+        <v>29</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="8">
+        <v>30</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/调度及腾讯字段解析.xlsx
+++ b/调度及腾讯字段解析.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\pyprj\stock2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB6BE59D-6FFE-440B-96D2-1642226BD9AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D001E5-68BB-49BD-9E43-048B1A432ABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{1FEC2500-66C5-48E4-A19C-F08A664BA3B3}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="188">
   <si>
     <t>市场状态</t>
   </si>
@@ -506,10 +506,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>腾讯的申万二级行业下个股的数据，调用7号，调度所有行业的明细数据到DB</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>腾讯实时个股数据。一次最多只能查询200只股票</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -665,6 +661,42 @@
   </si>
   <si>
     <t>巨潮的公司基本信息。批量获取，调用22（调度范围，动态：补充确实的股票）</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>fetch_plate_stocks_df</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>fetch_plate_stocks_db</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>腾讯的申万二级行业下个股的数据，调用8号，调度所有行业的明细数据到DB</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>腾讯的申万二级行业下个股的数据，调用31号，调度所有行业的明细数据到DB</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>_request</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>通用访问api获取数据。可以重试，使用代理等</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>腾讯的申万二级行业下个股的数据，指定行业，调用31号，返回df</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>天(fetch_plate_stocks_db)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>被替换</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1861,7 +1893,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2885176E-875C-420E-9376-FD5A86DAD936}">
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="8"/>
@@ -1876,12 +1908,12 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B1" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B2" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.25">
@@ -1901,16 +1933,16 @@
         <v>91</v>
       </c>
       <c r="F3" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="H3" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="G3" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="H3" s="9" t="s">
+      <c r="I3" s="9" t="s">
         <v>158</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>159</v>
       </c>
       <c r="J3" s="9" t="s">
         <v>113</v>
@@ -1979,7 +2011,7 @@
         <v>93</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -2042,7 +2074,7 @@
         <v>93</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -2079,7 +2111,7 @@
         <v>106</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>95</v>
@@ -2099,13 +2131,16 @@
         <v>108</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>93</v>
+        <v>186</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -2122,7 +2157,7 @@
         <v>109</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>95</v>
@@ -2142,16 +2177,16 @@
         <v>110</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>93</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -2171,16 +2206,16 @@
         <v>112</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J15" s="8" t="s">
         <v>114</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -2223,7 +2258,7 @@
         <v>93</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -2246,7 +2281,7 @@
         <v>93</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -2269,7 +2304,7 @@
         <v>93</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -2286,13 +2321,13 @@
         <v>125</v>
       </c>
       <c r="E20" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="F20" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="F20" s="8" t="s">
-        <v>168</v>
-      </c>
       <c r="J20" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K20" s="8" t="s">
         <v>130</v>
@@ -2349,7 +2384,7 @@
         <v>135</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K23" s="8" t="s">
         <v>136</v>
@@ -2363,13 +2398,13 @@
         <v>126</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J24" s="8" t="s">
         <v>114</v>
@@ -2380,25 +2415,25 @@
         <v>22</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J25" s="8" t="s">
         <v>114</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -2406,16 +2441,16 @@
         <v>23</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D26" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="E26" s="8" t="s">
         <v>147</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>148</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>117</v>
@@ -2426,28 +2461,28 @@
         <v>24</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>93</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -2455,22 +2490,22 @@
         <v>25</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>93</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -2478,16 +2513,16 @@
         <v>26</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>93</v>
@@ -2498,16 +2533,16 @@
         <v>27</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>125</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F30" s="8" t="s">
         <v>93</v>
@@ -2518,16 +2553,16 @@
         <v>28</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D31" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="E31" s="8" t="s">
         <v>170</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>171</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>93</v>
@@ -2538,39 +2573,102 @@
         <v>29</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D32" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="E32" s="8" t="s">
         <v>172</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>173</v>
       </c>
       <c r="F32" s="8" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="8">
         <v>30</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>93</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="8">
+        <v>31</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="8">
+        <v>32</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="8">
+        <v>33</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="J36" s="8" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/调度及腾讯字段解析.xlsx
+++ b/调度及腾讯字段解析.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\pyprj\stock2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D001E5-68BB-49BD-9E43-048B1A432ABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B14E814E-66E1-40EA-A41C-958A4616735B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{1FEC2500-66C5-48E4-A19C-F08A664BA3B3}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="192">
   <si>
     <t>市场状态</t>
   </si>
@@ -692,11 +692,27 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>天(fetch_plate_stocks_db)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>被替换</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>天(被fetch_plate_stocks_db替换)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>get_time_kline_df</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>腾讯的分时K线数据，每次只能调度一个qq_code到DB</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>get_time_detail_df</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>腾讯的成交明细数据，每次只能调度一个qq_code到DB，需要分页，如果是100表示全部，如果是99表示最后一页</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1893,7 +1909,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2885176E-875C-420E-9376-FD5A86DAD936}">
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="8"/>
@@ -2134,13 +2150,13 @@
         <v>181</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J12" s="8" t="s">
         <v>163</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -2669,6 +2685,46 @@
       </c>
       <c r="J36" s="8" t="s">
         <v>163</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="8">
+        <v>34</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="8">
+        <v>35</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>160</v>
       </c>
     </row>
   </sheetData>
